--- a/ARIE_Finance_Risk_Scoring_Model.xlsx
+++ b/ARIE_Finance_Risk_Scoring_Model.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="654">
   <si>
     <t xml:space="preserve">ARIE FINANCE LTD  —  CLIENT RISK SCORING MODEL</t>
   </si>
@@ -1209,7 +1209,7 @@
     <t xml:space="preserve">Ownership Consistency</t>
   </si>
   <si>
-    <t xml:space="preserve">Shareholdings must match UBOs declared in pre-screening</t>
+    <t xml:space="preserve">Shareholdings must match UBOs declared in application</t>
   </si>
   <si>
     <t xml:space="preserve">Client prompted: ownership does not match declared UBOs</t>
@@ -1239,7 +1239,7 @@
     <t xml:space="preserve">Director Consistency</t>
   </si>
   <si>
-    <t xml:space="preserve">Directors must match those declared in pre-screening</t>
+    <t xml:space="preserve">Directors must match those declared in application</t>
   </si>
   <si>
     <t xml:space="preserve">Client prompted: directors do not match application</t>
@@ -1455,7 +1455,7 @@
     <t xml:space="preserve">Nationality Match</t>
   </si>
   <si>
-    <t xml:space="preserve">Nationality must match the nationality declared in pre-screening</t>
+    <t xml:space="preserve">Nationality must match the nationality declared in application</t>
   </si>
   <si>
     <t xml:space="preserve">Client prompted: nationality mismatch detected</t>
@@ -1530,15 +1530,6 @@
     <t xml:space="preserve">Client prompted: bank reference letter is older than 3 months</t>
   </si>
   <si>
-    <t xml:space="preserve">Account Holder Name Match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account holder name must match the declared person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client prompted: name on bank reference does not match declared person</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bank Identification</t>
   </si>
   <si>
@@ -1587,13 +1578,10 @@
     <t xml:space="preserve">Client prompted: contracts appear unrelated to declared activities</t>
   </si>
   <si>
-    <t xml:space="preserve">Source of Wealth Evidence (High / Very High Risk only)</t>
-  </si>
-  <si>
     <t xml:space="preserve">SoW Consistency</t>
   </si>
   <si>
-    <t xml:space="preserve">Must support the source of wealth declared in pre-screening</t>
+    <t xml:space="preserve">Must support the source of wealth declared in application</t>
   </si>
   <si>
     <t xml:space="preserve">Client prompted: evidence does not match SoW declaration</t>
@@ -1608,15 +1596,12 @@
     <t xml:space="preserve">SoF Consistency</t>
   </si>
   <si>
-    <t xml:space="preserve">Must support the source of funds declared in pre-screening</t>
+    <t xml:space="preserve">Must support the source of funds declared in application</t>
   </si>
   <si>
     <t xml:space="preserve">Client prompted: evidence does not match SoF declaration</t>
   </si>
   <si>
-    <t xml:space="preserve">Bank Statements — Last 6 Months (High / Very High Risk only)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Statement Period</t>
   </si>
   <si>
@@ -1644,36 +1629,12 @@
     <t xml:space="preserve">Client prompted: there are gaps in the statement period</t>
   </si>
   <si>
-    <t xml:space="preserve">AML/CFT Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy Completeness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must cover CDD, suspicious transaction reporting, record-keeping, and training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client prompted: policy appears to be missing key sections</t>
-  </si>
-  <si>
     <t xml:space="preserve">Policy Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Should be reviewed within the last 12 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client prompted: policy may be outdated</t>
-  </si>
-  <si>
     <t xml:space="preserve">Applicability</t>
   </si>
   <si>
-    <t xml:space="preserve">Policy must be specific to the entity, not a generic template</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client informed: policy appears to be a generic template</t>
-  </si>
-  <si>
     <t xml:space="preserve">CHECK TYPE LEGEND</t>
   </si>
   <si>
@@ -1707,7 +1668,7 @@
     <t xml:space="preserve">AI-assisted compliance pipeline — agent definitions, trigger points, and outputs</t>
   </si>
   <si>
-    <t xml:space="preserve">ONBOARDING PIPELINE AGENTS</t>
+    <t xml:space="preserve">ONBOARDING AGENTS (1-5)</t>
   </si>
   <si>
     <t xml:space="preserve">Agent Name</t>
@@ -1728,231 +1689,247 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Account Risk Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detect suspicious sign-ups and prevent fraudulent or spam registrations before onboarding begins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client registration form submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disposable email domain detection
-IP geolocation mismatch
-VPN / TOR detection
-Repeated application detection
-Known fraud domain screening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Risk → Proceed
-Suspicious → Flag for monitoring
-Block → Registration denied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Screening Risk Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluate whether the client fits ARIE's risk appetite before full onboarding begins. Can eliminate 30-50% of unsuitable applicants early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After pre-screening form submission, during AI risk scoring phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prohibited sector screening
-Business model adequacy
-Geographic risk appetite
-Transaction volume reasonableness
-Payment corridor risk assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within Appetite → Proceed
-Review Required → Manual check
-Outside Appetite → Reject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate Data Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match and retrieve company data from public registries. Detect inconsistencies between registry data and client input.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company lookup / autofill stage (client enters company name or registration number)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company name match (registry vs input)
-Registration number verification
-Incorporation date cross-reference
-Registered address verification
-Director names consistency
-Active / dissolved status check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified → All data matched
-Possible Mismatch → Discrepancies flagged
-Multiple Matches → Client selects correct entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Narrative Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluate whether the business story is plausible and internally consistent. Detect high-risk onboarding profiles early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">During AI risk scoring phase (after pre-screening submission)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business description vs sector alignment
-Transaction volume vs company size
-Geography vs business model logic
-Revenue model plausibility
-Industry norm comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consistent → Proceed
-Needs Clarification → Flag for review
-Suspicious Profile → Escalate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document Intelligence Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatically read, validate, and cross-reference uploaded documents in real time. 61 verification checks across 16 document types.</t>
+    <t xml:space="preserve">Identity &amp; Document Integrity Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatically read, validate, and cross-reference uploaded documents in real time. Performs 66 automated checks across 16 document types. Verifies against public registries.</t>
   </si>
   <si>
     <t xml:space="preserve">Each document upload (real-time, immediate feedback)</t>
   </si>
   <si>
-    <t xml:space="preserve">OCR text extraction
-Document type identification
+    <t xml:space="preserve">OCR text extraction &amp; document type identification
 Expiry / validity detection
 Date checks (3mo / 6mo / 12mo / 18mo rules)
 Name matching (entity &amp; person)
-Document clarity / legibility
-Cross-document consistency
+Document clarity / legibility scoring
+Cross-document consistency checks
 Duplicate detection
+Registry verification (company name, reg number, directors, address)
 Completeness scoring</t>
   </si>
   <si>
     <t xml:space="preserve">Per-document: Pass / Warning / Fail with specific client prompts
 Aggregate: Document completeness score
-Cross-reference: Name match summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial Crime Intelligence Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse screening results, consolidate hits, remove false positives, and summarise real risks. Saves compliance officers significant time.</t>
+Cross-reference: Name &amp; registry match summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Structure &amp; UBO Mapping Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyse declared ownership structures, trace beneficial ownership chains, and identify ultimate beneficial owners (UBOs). Detect complex or layered structures requiring enhanced due diligence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After application form submission, during AI risk scoring phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ownership chain tracing (direct &amp; indirect)
+UBO identification (≥25% threshold)
+Multi-layered entity detection
+Circular ownership detection
+Nominee / trust identification
+Shareholder register cross-reference
+Structure chart validation
+PEP/sanctions check on all identified UBOs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple Structure → Proceed
+Complex Structure → Flag for enhanced review
+Opaque / Circular → Escalate to compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Model Plausibility Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluate whether the business story is plausible and internally consistent. Compare against industry benchmarks and detect high-risk onboarding profiles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During AI risk scoring phase (after application submission)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business description vs sector alignment
+Transaction volume vs company size benchmarking
+Geography vs business model logic
+Revenue model plausibility
+Industry norm comparison
+Payment corridor risk assessment
+Source of funds vs business activity consistency
+Source of wealth vs entity profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consistent → Proceed
+Needs Clarification → Flag specific areas
+Suspicious Profile → Escalate with reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinCrime Screening Interpretation Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyse screening results from sanctions, PEP, and adverse media databases. Consolidate hits, remove false positives, rank severity, and summarise real risks.</t>
   </si>
   <si>
     <t xml:space="preserve">During AI risk scoring phase</t>
   </si>
   <si>
-    <t xml:space="preserve">Global sanctions (UN, EU, OFAC, HMT)
-PEP database (World-Check, Dow Jones)
-Adverse media (100,000+ sources)
+    <t xml:space="preserve">Global sanctions screening (UN, EU, OFAC, HMT)
+PEP database analysis (World-Check, Dow Jones)
+Adverse media scanning (100,000+ sources)
 False positive analysis &amp; reduction
-Hit severity ranking
-Consolidated risk summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Clear → No escalation
-Review Required → True positive identified
-Escalate → Confirmed match (sanctions/PEP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source of Funds Analysis Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluate the plausibility of the client's financial explanation. Identify financial crime risks early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SoF explanation vs business activity
-SoF vs expected transaction volumes
-SoW consistency with entity profile
-Documentation sufficiency assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supported → SoF/SoW plausible
-Partially Supported → Additional docs may be needed
-Unsupported → Escalate to compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk Decision Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combine all signals from all agents into a structured risk recommendation. Assign onboarding lane. AI never approves — only recommends.</t>
+Hit severity ranking &amp; categorisation
+Consolidated risk narrative generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Clear → No escalation needed
+Review Required → True positive identified with context
+Escalate → Confirmed match (sanctions/PEP) with evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance Memo &amp; Risk Recommendation Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combine all signals from all agents into a structured compliance memo with risk recommendation. Assign risk score and onboarding lane. AI never approves — only recommends.</t>
   </si>
   <si>
     <t xml:space="preserve">End of AI risk scoring phase (after all other agents complete)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jurisdiction risk (Dimension 2)
+    <t xml:space="preserve">5-dimension weighted composite scoring
+Jurisdiction risk (Dimension 2)
 Industry risk (Dimension 4)
 Ownership complexity (Dimension 1)
 Screening results integration
 Document completeness signal
-Source of funds consistency
-5-dimension weighted composite score</t>
+Business plausibility assessment
+Complete compliance memo generation</t>
   </si>
   <si>
     <t xml:space="preserve">Risk Score (0-100) + Level (Low/Medium/High/Very High)
-Onboarding Lane:
-  Fast Lane (Low risk)
-  Standard Review (Medium)
-  Enhanced Due Diligence (High/Very High)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance Memo Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatically generate a structured case summary for compliance officers, eliminating manual report writing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client submits final application (after pre-submission review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client overview generation
-Ownership structure summary
-Screening summary (sanctions/PEP/adverse media)
-Risk driver identification &amp; colour-coding
-Lane-specific recommendation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete compliance memo containing:
-  Client profile
-  Ownership structure
-  Screening results
-  Risk drivers
-  AI recommendation &amp; assigned lane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continuous Risk Monitoring Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-onboarding lifecycle monitoring. Detect changes in risk profile after account is active.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ongoing (scheduled periodic scans + event-driven alerts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New adverse media detection
-Sanctions list updates
-Ownership change detection
-Unusual activity pattern analysis
-Periodic re-screening (annual/biannual)</t>
+Decision Routing:
+  LOW/MEDIUM → KYC &amp; Documents stage
+  HIGH/VERY HIGH → Compliance review + notification
+Full compliance memo with all findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic Review Preparation Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Track review schedules, identify expired documents, and prepare review packages for compliance officers. Automate periodic review lifecycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled (based on risk-level review cycles: annual/biannual/quarterly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review cycle tracking by risk level
+Expired document identification
+Document renewal deadline monitoring
+Review package preparation
+Priority scoring for overdue reviews
+Client notification triggers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up to Date → No action needed
+Review Due → Package prepared for compliance
+Documents Pending → Client notified to upload
+Overdue → Escalated to compliance manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adverse Media &amp; PEP Monitoring Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuous monitoring of adverse media and PEP databases for all active clients. Detect new risks that emerge after onboarding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ongoing (daily automated scans + event-driven alerts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New adverse media detection (100,000+ sources)
+Sanctions list update monitoring (UN, EU, OFAC, HMT)
+PEP status change detection
+New directorship / association alerts
+Severity classification &amp; false positive filtering
+Historical trend analysis</t>
   </si>
   <si>
     <t xml:space="preserve">No Change → Continue monitoring
-Alert → Risk change detected
-Escalate → Immediate compliance review</t>
+New Alert → Risk change detected with context
+Escalate → Immediate compliance review required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behaviour &amp; Risk Drift Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitor changes in client activity patterns and risk profile over time. Detect drift between onboarded profile and actual behaviour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ongoing (event-driven + periodic analysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction pattern vs declared volumes
+Geographic activity vs declared corridors
+New product/service usage detection
+Counterparty risk changes
+Volume spike / drop analysis
+Seasonal pattern deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within Expected → Continue monitoring
+Drift Detected → Flag for review with analysis
+Significant Deviation → Escalate with full report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory Impact Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitor regulatory changes across relevant jurisdictions and assess impact on existing client portfolio. Proactively flag clients affected by new regulations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event-driven (new regulation / guidance published)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory change detection (FSC, BoM, FATF, EU)
+Client portfolio impact assessment
+Jurisdiction-specific rule mapping
+Licence requirement change monitoring
+Compliance deadline tracking
+Gap analysis (current vs new requirements)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Impact → Log for records
+Minor Impact → Update client risk profile
+Significant Impact → Compliance action required with deadline</t>
   </si>
   <si>
     <t xml:space="preserve">Future Phase</t>
   </si>
   <si>
+    <t xml:space="preserve">Ongoing Compliance Review Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate periodic compliance review reports consolidating all monitoring signals. Provide holistic view of client risk status over time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled (aligned with periodic review cycles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All monitoring agent signal consolidation
+Risk score trend analysis
+Incident history compilation
+Document status summary
+Compliance action tracking
+Recommendation generation for review outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Risk → Maintain current status
+Elevated Risk → Enhanced monitoring recommended
+High Risk → Relationship review / exit consideration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONGOING MONITORING AGENTS (6-10)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI COMPLIANCE PIPELINE FLOW</t>
   </si>
   <si>
@@ -1968,31 +1945,32 @@
     <t xml:space="preserve">Registration &amp; Login</t>
   </si>
   <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
     <t xml:space="preserve">→</t>
   </si>
   <si>
-    <t xml:space="preserve">Company Lookup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Screening Form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
+    <t xml:space="preserve">Application Form</t>
   </si>
   <si>
     <t xml:space="preserve">AI Risk Scoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-Screening Risk Agent + Business Narrative Agent + Financial Crime Agent + Source of Funds Agent + Risk Decision Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pricing Acceptance</t>
+    <t xml:space="preserve">Corporate Structure &amp; UBO Mapping + Business Model Plausibility + FinCrime Screening Interpretation + Compliance Memo &amp; Risk Recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW/MEDIUM Risk → KYC &amp; Documents
+HIGH/VERY HIGH Risk → Compliance Review + Notification</t>
   </si>
   <si>
     <t xml:space="preserve">KYC Document Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">Document Intelligence Agent (61 checks)</t>
+    <t xml:space="preserve">Identity &amp; Document Integrity Agent (66 checks)</t>
   </si>
   <si>
     <t xml:space="preserve">Pre-Submission Review</t>
@@ -2010,16 +1988,16 @@
     <t xml:space="preserve">Account Activated</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuous Monitoring Agent (Future)</t>
+    <t xml:space="preserve">Monitoring Agents (6-10) begin lifecycle monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">STRATEGIC ADVANTAGE</t>
   </si>
   <si>
-    <t xml:space="preserve">With this AI-assisted compliance pipeline, ARIE Finance can realistically achieve low-risk onboarding decisions in 24 hours or less — extremely competitive compared to traditional banks and payment institutions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total AI Agents: 10 (9 Live + 1 Future Phase)  |  Total AI Verification Checks: 61  |  Document Types Covered: 16</t>
+    <t xml:space="preserve">With this AI-assisted compliance pipeline, ARIE Finance can realistically achieve low-risk onboarding decisions in 24 hours or less — extremely competitive compared to traditional banks and payment institutions. The 5 monitoring agents provide continuous lifecycle risk management post-onboarding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total AI Agents: 10 (5 Onboarding + 5 Monitoring)  |  Total AI Verification Checks: 66  |  Document Types Covered: 16</t>
   </si>
   <si>
     <t xml:space="preserve">ARIE FINANCE LTD — RISK SCORING MODEL: METHODOLOGY</t>
@@ -2134,7 +2112,7 @@
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="63">
+  <fonts count="62">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2489,14 +2467,6 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -2576,8 +2546,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2899,7 +2869,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3188,19 +3158,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="19" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="22" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="22" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3216,11 +3186,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3228,7 +3198,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3236,67 +3206,75 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="57" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="59" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="59" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="61" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3485,7 +3463,7 @@
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFCC0000"/>
-      <rgbColor rgb="FFFFF7ED"/>
+      <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFF5F0E6"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -3503,7 +3481,7 @@
       <rgbColor rgb="FFFEF9E7"/>
       <rgbColor rgb="FFE3F2FD"/>
       <rgbColor rgb="FF374151"/>
-      <rgbColor rgb="FFCA6F1E"/>
+      <rgbColor rgb="FFFFEBEE"/>
       <rgbColor rgb="FF1565C0"/>
       <rgbColor rgb="FFD0D5DD"/>
       <rgbColor rgb="FF000080"/>
@@ -3514,7 +3492,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF1A75CB"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFEBEE"/>
+      <rgbColor rgb="FFFFF7ED"/>
       <rgbColor rgb="FFD5E8F0"/>
       <rgbColor rgb="FFD5F5E3"/>
       <rgbColor rgb="FFFFF3E0"/>
@@ -3526,7 +3504,7 @@
       <rgbColor rgb="FFEEF2FA"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFFAE5D3"/>
-      <rgbColor rgb="FFD97706"/>
+      <rgbColor rgb="FFCA6F1E"/>
       <rgbColor rgb="FFE65100"/>
       <rgbColor rgb="FF5A6A7A"/>
       <rgbColor rgb="FFB8955A"/>
@@ -3750,6 +3728,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>2</v>
@@ -4308,6 +4287,7 @@
       <c r="D50" s="29"/>
       <c r="E50" s="29"/>
     </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="30" t="s">
         <v>52</v>
@@ -7909,6 +7889,7 @@
       <c r="E2" s="57"/>
       <c r="F2" s="57"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
         <v>355</v>
@@ -8591,6 +8572,7 @@
         <v>463</v>
       </c>
     </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="58" t="s">
         <v>464</v>
@@ -8863,7 +8845,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="67" t="n">
         <v>49</v>
       </c>
@@ -8888,18 +8870,10 @@
         <v>50</v>
       </c>
       <c r="B58" s="67"/>
-      <c r="C58" s="67" t="s">
-        <v>501</v>
-      </c>
-      <c r="D58" s="67" t="s">
-        <v>502</v>
-      </c>
-      <c r="E58" s="67" t="s">
-        <v>365</v>
-      </c>
-      <c r="F58" s="67" t="s">
-        <v>503</v>
-      </c>
+      <c r="C58" s="67"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="67"/>
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="n">
@@ -8907,16 +8881,16 @@
       </c>
       <c r="B59" s="72"/>
       <c r="C59" s="69" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D59" s="69" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E59" s="73" t="s">
         <v>369</v>
       </c>
       <c r="F59" s="71" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8925,16 +8899,16 @@
       </c>
       <c r="B60" s="74"/>
       <c r="C60" s="69" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D60" s="69" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E60" s="73" t="s">
         <v>369</v>
       </c>
       <c r="F60" s="71" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8943,16 +8917,16 @@
       </c>
       <c r="B61" s="74"/>
       <c r="C61" s="69" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D61" s="69" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E61" s="75" t="s">
         <v>373</v>
       </c>
       <c r="F61" s="71" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8960,7 +8934,7 @@
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="76" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B63" s="77"/>
     </row>
@@ -8968,9 +8942,7 @@
       <c r="A64" s="59" t="s">
         <v>356</v>
       </c>
-      <c r="B64" s="77" t="s">
-        <v>357</v>
-      </c>
+      <c r="B64" s="77"/>
       <c r="C64" s="59" t="s">
         <v>358</v>
       </c>
@@ -8989,19 +8961,19 @@
         <v>54</v>
       </c>
       <c r="B65" s="78" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C65" s="62" t="s">
         <v>363</v>
       </c>
       <c r="D65" s="62" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E65" s="63" t="s">
         <v>365</v>
       </c>
       <c r="F65" s="62" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9010,16 +8982,16 @@
       </c>
       <c r="B66" s="78"/>
       <c r="C66" s="62" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D66" s="62" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E66" s="60" t="s">
         <v>369</v>
       </c>
       <c r="F66" s="62" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9044,20 +9016,18 @@
       <c r="A68" s="60" t="n">
         <v>57</v>
       </c>
-      <c r="B68" s="79" t="s">
-        <v>520</v>
-      </c>
+      <c r="B68" s="79"/>
       <c r="C68" s="62" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D68" s="62" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E68" s="60" t="s">
         <v>369</v>
       </c>
       <c r="F68" s="62" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9069,7 +9039,7 @@
         <v>371</v>
       </c>
       <c r="D69" s="62" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E69" s="64" t="s">
         <v>373</v>
@@ -9083,19 +9053,19 @@
         <v>59</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C70" s="62" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D70" s="62" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E70" s="60" t="s">
         <v>369</v>
       </c>
       <c r="F70" s="62" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9107,7 +9077,7 @@
         <v>371</v>
       </c>
       <c r="D71" s="62" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E71" s="64" t="s">
         <v>373</v>
@@ -9120,41 +9090,39 @@
       <c r="A72" s="60" t="n">
         <v>61</v>
       </c>
-      <c r="B72" s="61" t="s">
-        <v>529</v>
-      </c>
+      <c r="B72" s="61"/>
       <c r="C72" s="62" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D72" s="62" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E72" s="66" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F72" s="62" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="60" t="n">
         <v>62</v>
       </c>
       <c r="B73" s="80"/>
       <c r="C73" s="62" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D73" s="62" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E73" s="63" t="s">
         <v>365</v>
       </c>
       <c r="F73" s="62" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="60" t="n">
         <v>63</v>
       </c>
@@ -9163,34 +9131,24 @@
         <v>378</v>
       </c>
       <c r="D74" s="62" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E74" s="64" t="s">
         <v>373</v>
       </c>
       <c r="F74" s="62" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="60" t="n">
         <v>64</v>
       </c>
-      <c r="B75" s="60" t="s">
-        <v>539</v>
-      </c>
-      <c r="C75" s="60" t="s">
-        <v>540</v>
-      </c>
-      <c r="D75" s="60" t="s">
-        <v>541</v>
-      </c>
-      <c r="E75" s="60" t="s">
-        <v>369</v>
-      </c>
-      <c r="F75" s="60" t="s">
-        <v>542</v>
-      </c>
+      <c r="B75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="60" t="n">
@@ -9198,17 +9156,11 @@
       </c>
       <c r="B76" s="80"/>
       <c r="C76" s="62" t="s">
-        <v>543</v>
-      </c>
-      <c r="D76" s="62" t="s">
-        <v>544</v>
-      </c>
-      <c r="E76" s="62" t="s">
-        <v>400</v>
-      </c>
-      <c r="F76" s="62" t="s">
-        <v>545</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="D76" s="62"/>
+      <c r="E76" s="62"/>
+      <c r="F76" s="62"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="60" t="n">
@@ -9216,17 +9168,11 @@
       </c>
       <c r="B77" s="79"/>
       <c r="C77" s="62" t="s">
-        <v>546</v>
-      </c>
-      <c r="D77" s="62" t="s">
-        <v>547</v>
-      </c>
-      <c r="E77" s="62" t="s">
-        <v>369</v>
-      </c>
-      <c r="F77" s="62" t="s">
-        <v>548</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="D77" s="62"/>
+      <c r="E77" s="62"/>
+      <c r="F77" s="62"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C78" s="81"/>
@@ -9242,30 +9188,30 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="76" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="C80" s="81"/>
       <c r="D80" s="81"/>
       <c r="E80" s="81"/>
       <c r="F80" s="81"/>
     </row>
-    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="82" t="s">
         <v>365</v>
       </c>
       <c r="C81" s="83" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D81" s="84"/>
       <c r="E81" s="84"/>
       <c r="F81" s="84"/>
     </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="85" t="s">
         <v>388</v>
       </c>
       <c r="C82" s="83" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="D82" s="84"/>
       <c r="E82" s="84"/>
@@ -9273,10 +9219,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="86" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="C83" s="83" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="D83" s="84"/>
       <c r="E83" s="84"/>
@@ -9287,33 +9233,31 @@
         <v>373</v>
       </c>
       <c r="C84" s="83" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="D84" s="84"/>
       <c r="E84" s="84"/>
       <c r="F84" s="84"/>
     </row>
-    <row r="85" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="88" t="s">
         <v>369</v>
       </c>
       <c r="C85" s="83" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D85" s="84"/>
       <c r="E85" s="84"/>
       <c r="F85" s="84"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="89" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="90" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -9379,7 +9323,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="91" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="B1" s="91"/>
       <c r="C1" s="91"/>
@@ -9390,7 +9334,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="57" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
@@ -9401,7 +9345,7 @@
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
@@ -9415,469 +9359,441 @@
         <v>356</v>
       </c>
       <c r="B5" s="59" t="s">
+        <v>548</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>549</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>550</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>551</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>552</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>554</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>555</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>556</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>558</v>
+      </c>
+      <c r="G6" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>561</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="D7" s="62" t="s">
         <v>562</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="E7" s="62" t="s">
         <v>563</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="F7" s="62" t="s">
         <v>564</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="G7" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="61" t="s">
         <v>565</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="C8" s="62" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="61" t="s">
+      <c r="D8" s="62" t="s">
         <v>567</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="E8" s="62" t="s">
         <v>568</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="F8" s="62" t="s">
         <v>569</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="G8" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="61" t="s">
         <v>570</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="C9" s="62" t="s">
         <v>571</v>
       </c>
-      <c r="G6" s="93" t="s">
+      <c r="D9" s="62" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="92" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="61" t="s">
+      <c r="E9" s="62" t="s">
         <v>573</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="F9" s="62" t="s">
         <v>574</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="G9" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="61" t="s">
         <v>575</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="C10" s="62" t="s">
         <v>576</v>
       </c>
-      <c r="F7" s="62" t="s">
+      <c r="D10" s="62" t="s">
         <v>577</v>
       </c>
-      <c r="G7" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="92" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="61" t="s">
+      <c r="E10" s="62" t="s">
         <v>578</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="F10" s="62" t="s">
         <v>579</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="G10" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="61" t="s">
         <v>580</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="C11" s="62" t="s">
         <v>581</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="D11" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="G8" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="92" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="61" t="s">
+      <c r="E11" s="62" t="s">
         <v>583</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="F11" s="62" t="s">
         <v>584</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="G11" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="C12" s="62" t="s">
         <v>586</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="D12" s="62" t="s">
         <v>587</v>
       </c>
-      <c r="G9" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="92" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="61" t="s">
+      <c r="E12" s="62" t="s">
         <v>588</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="F12" s="62" t="s">
         <v>589</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="G12" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="61" t="s">
         <v>590</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="C13" s="62" t="s">
         <v>591</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="D13" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="G10" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="92" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="61" t="s">
+      <c r="E13" s="62" t="s">
         <v>593</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="F13" s="62" t="s">
         <v>594</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="G13" s="92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="61" t="s">
         <v>595</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="C14" s="62" t="s">
         <v>596</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="D14" s="62" t="s">
         <v>597</v>
       </c>
-      <c r="G11" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="92" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="61" t="s">
+      <c r="E14" s="62" t="s">
         <v>598</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="F14" s="62" t="s">
         <v>599</v>
       </c>
-      <c r="D12" s="62" t="s">
-        <v>595</v>
-      </c>
-      <c r="E12" s="62" t="s">
+      <c r="G14" s="92" t="s">
         <v>600</v>
       </c>
-      <c r="F12" s="62" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="61" t="s">
         <v>601</v>
       </c>
-      <c r="G12" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="92" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="61" t="s">
+      <c r="C15" s="62" t="s">
         <v>602</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="D15" s="62" t="s">
         <v>603</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="E15" s="62" t="s">
         <v>604</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="F15" s="62" t="s">
         <v>605</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="G15" s="93" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="94" t="s">
         <v>606</v>
       </c>
-      <c r="G13" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="92" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="61" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="95" t="s">
         <v>607</v>
       </c>
-      <c r="C14" s="62" t="s">
-        <v>608</v>
-      </c>
-      <c r="D14" s="62" t="s">
-        <v>609</v>
-      </c>
-      <c r="E14" s="62" t="s">
-        <v>610</v>
-      </c>
-      <c r="F14" s="62" t="s">
-        <v>611</v>
-      </c>
-      <c r="G14" s="93" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="92" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>612</v>
-      </c>
-      <c r="C15" s="62" t="s">
-        <v>613</v>
-      </c>
-      <c r="D15" s="62" t="s">
-        <v>614</v>
-      </c>
-      <c r="E15" s="62" t="s">
-        <v>615</v>
-      </c>
-      <c r="F15" s="62" t="s">
-        <v>616</v>
-      </c>
-      <c r="G15" s="94" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="58" t="s">
-        <v>618</v>
-      </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59"/>
-      <c r="B19" s="59" t="s">
-        <v>619</v>
-      </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59" t="s">
-        <v>620</v>
-      </c>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
+      <c r="B19" s="96" t="s">
+        <v>608</v>
+      </c>
+      <c r="D19" s="96" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="95" t="s">
-        <v>621</v>
+      <c r="A20" s="60" t="s">
+        <v>610</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="C20" s="61"/>
       <c r="D20" s="83" t="s">
-        <v>567</v>
+        <v>612</v>
       </c>
       <c r="E20" s="83"/>
       <c r="F20" s="83"/>
       <c r="G20" s="83"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="95" t="s">
-        <v>623</v>
+      <c r="A21" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C21" s="61"/>
       <c r="D21" s="83" t="s">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="E21" s="83"/>
       <c r="F21" s="83"/>
       <c r="G21" s="83"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="95" t="s">
-        <v>623</v>
+      <c r="A22" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="83" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="E22" s="83"/>
       <c r="F22" s="83"/>
       <c r="G22" s="83"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="95" t="s">
-        <v>623</v>
+      <c r="A23" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C23" s="61"/>
       <c r="D23" s="83" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E23" s="83"/>
       <c r="F23" s="83"/>
       <c r="G23" s="83"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="95" t="s">
-        <v>623</v>
+      <c r="A24" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C24" s="61"/>
       <c r="D24" s="83" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E24" s="83"/>
       <c r="F24" s="83"/>
       <c r="G24" s="83"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="95" t="s">
-        <v>623</v>
+      <c r="A25" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="C25" s="61"/>
       <c r="D25" s="83" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="E25" s="83"/>
       <c r="F25" s="83"/>
       <c r="G25" s="83"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="95" t="s">
-        <v>623</v>
+      <c r="A26" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C26" s="61"/>
       <c r="D26" s="83" t="s">
-        <v>626</v>
+        <v>575</v>
       </c>
       <c r="E26" s="83"/>
       <c r="F26" s="83"/>
       <c r="G26" s="83"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="B27" s="61" t="s">
         <v>623</v>
-      </c>
-      <c r="B27" s="61" t="s">
-        <v>633</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="83" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="E27" s="83"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="95" t="s">
-        <v>623</v>
+      <c r="A28" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="C28" s="61"/>
       <c r="D28" s="83" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="E28" s="83"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="95" t="s">
-        <v>623</v>
-      </c>
-      <c r="B29" s="61" t="s">
-        <v>636</v>
-      </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="83" t="s">
-        <v>637</v>
-      </c>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="61"/>
+      <c r="D29" s="83"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="96" t="s">
-        <v>638</v>
-      </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
+      <c r="A32" s="98" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="97" t="s">
-        <v>639</v>
-      </c>
-      <c r="B33" s="97"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
+      <c r="A33" s="99" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="98" t="s">
-        <v>640</v>
-      </c>
-      <c r="B35" s="98"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98"/>
+      <c r="A35" s="100" t="s">
+        <v>629</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="22">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:G19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="B21:C21"/>
@@ -9896,11 +9812,6 @@
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9925,158 +9836,159 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="99" t="s">
-        <v>641</v>
-      </c>
-      <c r="B1" s="99"/>
+      <c r="A1" s="101" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1" s="101"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="B2" s="3"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="100" t="s">
-        <v>644</v>
-      </c>
-      <c r="B5" s="100"/>
+      <c r="A5" s="102" t="s">
+        <v>633</v>
+      </c>
+      <c r="B5" s="102"/>
     </row>
     <row r="6" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="100" t="s">
-        <v>646</v>
-      </c>
-      <c r="B8" s="100"/>
+      <c r="A8" s="102" t="s">
+        <v>635</v>
+      </c>
+      <c r="B8" s="102"/>
     </row>
     <row r="9" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="100" t="s">
-        <v>648</v>
-      </c>
-      <c r="B11" s="100"/>
+      <c r="A11" s="102" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" s="102"/>
     </row>
     <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="B13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="100" t="s">
-        <v>650</v>
-      </c>
-      <c r="B14" s="100"/>
+      <c r="A14" s="102" t="s">
+        <v>639</v>
+      </c>
+      <c r="B14" s="102"/>
     </row>
     <row r="15" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="B16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="100" t="s">
-        <v>652</v>
-      </c>
-      <c r="B17" s="100"/>
+      <c r="A17" s="102" t="s">
+        <v>641</v>
+      </c>
+      <c r="B17" s="102"/>
     </row>
     <row r="18" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="B19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="100" t="s">
-        <v>654</v>
-      </c>
-      <c r="B20" s="100"/>
+      <c r="A20" s="102" t="s">
+        <v>643</v>
+      </c>
+      <c r="B20" s="102"/>
     </row>
     <row r="21" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="B22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="100" t="s">
-        <v>656</v>
-      </c>
-      <c r="B23" s="100"/>
+      <c r="A23" s="102" t="s">
+        <v>645</v>
+      </c>
+      <c r="B23" s="102"/>
     </row>
     <row r="24" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="B25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="100" t="s">
-        <v>658</v>
-      </c>
-      <c r="B26" s="100"/>
+      <c r="A26" s="102" t="s">
+        <v>647</v>
+      </c>
+      <c r="B26" s="102"/>
     </row>
     <row r="27" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="100" t="s">
-        <v>660</v>
-      </c>
-      <c r="B29" s="100"/>
+      <c r="A29" s="102" t="s">
+        <v>649</v>
+      </c>
+      <c r="B29" s="102"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="B31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="100" t="s">
-        <v>662</v>
-      </c>
-      <c r="B32" s="100"/>
+      <c r="A32" s="102" t="s">
+        <v>651</v>
+      </c>
+      <c r="B32" s="102"/>
     </row>
     <row r="33" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="B34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="100" t="s">
-        <v>664</v>
-      </c>
-      <c r="B35" s="100"/>
+      <c r="A35" s="102" t="s">
+        <v>653</v>
+      </c>
+      <c r="B35" s="102"/>
     </row>
     <row r="36" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
